--- a/figs/Fig4_Perturbseq/output/SuppTable_random_sets.xlsx
+++ b/figs/Fig4_Perturbseq/output/SuppTable_random_sets.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Random sets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Other matching methods" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Random sets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Other matching methods" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -536,7 +536,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Source: figs/Fig4_Perturbseq/output/geneset_random_null.csv (figs/Fig4_Perturbseq/analysis/fig4_random_set_null.py; seed 1) and fig4_other_methods_summary.csv (figs/Fig4_Perturbseq/analysis/fig4_other_methods.py; the same draws); table made by figs/Fig4_Perturbseq/analysis/supp_table_random_sets.py on 2026-10-16.</t>
+          <t>Source: figs/Fig4_Perturbseq/output/geneset_random_null.csv (figs/Fig4_Perturbseq/analysis/fig4_random_set_null.py; seed 1) and fig4_other_methods_summary.csv (figs/Fig4_Perturbseq/analysis/fig4_other_methods.py; the same draws); table made by figs/Fig4_Perturbseq/analysis/supp_table_random_sets.py on 2026-10-17.</t>
         </is>
       </c>
     </row>

--- a/figs/Fig4_Perturbseq/output/SuppTable_random_sets.xlsx
+++ b/figs/Fig4_Perturbseq/output/SuppTable_random_sets.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Random sets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Other matching methods" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Random sets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Other matching methods" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -536,7 +536,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Source: figs/Fig4_Perturbseq/output/geneset_random_null.csv (figs/Fig4_Perturbseq/analysis/fig4_random_set_null.py; seed 1) and fig4_other_methods_summary.csv (figs/Fig4_Perturbseq/analysis/fig4_other_methods.py; the same draws); table made by figs/Fig4_Perturbseq/analysis/supp_table_random_sets.py on 2026-10-17.</t>
+          <t>Source: figs/Fig4_Perturbseq/output/geneset_random_null.csv (figs/Fig4_Perturbseq/analysis/fig4_random_set_null.py; seed 1) and fig4_other_methods_summary.csv (figs/Fig4_Perturbseq/analysis/fig4_other_methods.py; the same draws); table made by figs/Fig4_Perturbseq/analysis/supp_table_random_sets.py on 2026-10-19.</t>
         </is>
       </c>
     </row>

--- a/figs/Fig4_Perturbseq/output/SuppTable_random_sets.xlsx
+++ b/figs/Fig4_Perturbseq/output/SuppTable_random_sets.xlsx
@@ -505,7 +505,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>&lt;gene&gt;: % from the opposed end — position of the knock-out counted from the knock-out most opposed to the stress response (1), as a percentage of the knock-outs ranked (as in Fig. 4e; below 50, the opposed side).</t>
+          <t>&lt;gene&gt;: % from the opposed end — position of the knock-out counted from the knock-out most opposed to the stress response (1), as a percentage of the knock-outs ranked (below 50, the opposed side).</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Source: figs/Fig4_Perturbseq/output/geneset_random_null.csv (figs/Fig4_Perturbseq/analysis/fig4_random_set_null.py; seed 1) and fig4_other_methods_summary.csv (figs/Fig4_Perturbseq/analysis/fig4_other_methods.py; the same draws); table made by figs/Fig4_Perturbseq/analysis/supp_table_random_sets.py on 2026-10-19.</t>
+          <t>Source: figs/Fig4_Perturbseq/output/geneset_random_null.csv (figs/Fig4_Perturbseq/analysis/fig4_random_set_null.py; seed 1) and fig4_other_methods_summary.csv (figs/Fig4_Perturbseq/analysis/fig4_other_methods.py; the same draws); table made by figs/Fig4_Perturbseq/analysis/supp_table_random_sets.py on 2026-10-21.</t>
         </is>
       </c>
     </row>
